--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.79452198226252</v>
+        <v>3.054109822117659</v>
       </c>
       <c r="D2" t="n">
-        <v>65.98847704224099</v>
+        <v>10.72312751936416</v>
       </c>
       <c r="E2" t="n">
-        <v>6.205059480076009</v>
+        <v>1.008322165512352</v>
       </c>
       <c r="F2" t="n">
-        <v>19.15922498510269</v>
+        <v>3.113374060079186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.80650914614596</v>
+        <v>5.331057736248718</v>
       </c>
       <c r="D3" t="n">
-        <v>33.31608675122935</v>
+        <v>5.41386409707477</v>
       </c>
       <c r="E3" t="n">
-        <v>6.205059480076009</v>
+        <v>1.008322165512352</v>
       </c>
       <c r="F3" t="n">
-        <v>19.15922498510269</v>
+        <v>3.113374060079186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.70045713609388</v>
+        <v>3.363824284615255</v>
       </c>
       <c r="D4" t="n">
-        <v>20.47647439055156</v>
+        <v>3.327427088464629</v>
       </c>
       <c r="E4" t="n">
-        <v>6.205059480076009</v>
+        <v>1.008322165512352</v>
       </c>
       <c r="F4" t="n">
-        <v>19.15922498510269</v>
+        <v>3.113374060079186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
